--- a/test-data/users.xlsx
+++ b/test-data/users.xlsx
@@ -1,41 +1,128 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Automation Project\WebWish 2\test-data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F6DEFE-77CF-4589-A9C5-05691260E177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>environment</t>
+  </si>
+  <si>
+    <t>enabled</t>
+  </si>
+  <si>
+    <t>SACH</t>
+  </si>
+  <si>
+    <t>Sachin@578</t>
+  </si>
+  <si>
+    <t>sach@example.com</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>MoneY@#369</t>
+  </si>
+  <si>
+    <t>testuser@example.com</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>dev</t>
+  </si>
+  <si>
+    <t>STAGE_USER</t>
+  </si>
+  <si>
+    <t>Stage@123</t>
+  </si>
+  <si>
+    <t>stageuser@example.com</t>
+  </si>
+  <si>
+    <t>stage</t>
+  </si>
+  <si>
+    <t>PROD_USER</t>
+  </si>
+  <si>
+    <t>Prod@123</t>
+  </si>
+  <si>
+    <t>produser@example.com</t>
+  </si>
+  <si>
+    <t>prod</t>
+  </si>
+  <si>
+    <t>DUMMY</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>wrongpass</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>CR01</t>
+  </si>
+  <si>
+    <t>cr01@example.com</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -44,15 +131,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +153,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,173 +514,316 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>index</v>
-      </c>
-      <c r="B1" t="str">
-        <v>username</v>
-      </c>
-      <c r="C1" t="str">
-        <v>password</v>
-      </c>
-      <c r="D1" t="str">
-        <v>email</v>
-      </c>
-      <c r="E1" t="str">
-        <v>role</v>
-      </c>
-      <c r="F1" t="str">
-        <v>environment</v>
-      </c>
-      <c r="G1" t="str">
-        <v>enabled</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="str">
-        <v>SACH</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Sachin@578</v>
-      </c>
-      <c r="D2" t="str">
-        <v>sach@example.com</v>
-      </c>
-      <c r="E2" t="str">
-        <v>admin</v>
-      </c>
-      <c r="F2" t="str">
-        <v>all</v>
-      </c>
-      <c r="G2" t="str">
-        <v>TRUE</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="str">
-        <v>ABC</v>
-      </c>
-      <c r="C3" t="str">
-        <v>MoneY@#369</v>
-      </c>
-      <c r="D3" t="str">
-        <v>testuser@example.com</v>
-      </c>
-      <c r="E3" t="str">
-        <v>user</v>
-      </c>
-      <c r="F3" t="str">
-        <v>dev</v>
-      </c>
-      <c r="G3" t="str">
-        <v>TRUE</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="str">
-        <v>STAGE_USER</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Stage@123</v>
-      </c>
-      <c r="D4" t="str">
-        <v>stageuser@example.com</v>
-      </c>
-      <c r="E4" t="str">
-        <v>user</v>
-      </c>
-      <c r="F4" t="str">
-        <v>stage</v>
-      </c>
-      <c r="G4" t="str">
-        <v>TRUE</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="str">
-        <v>PROD_USER</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Prod@123</v>
-      </c>
-      <c r="D5" t="str">
-        <v>produser@example.com</v>
-      </c>
-      <c r="E5" t="str">
-        <v>user</v>
-      </c>
-      <c r="F5" t="str">
-        <v>prod</v>
-      </c>
-      <c r="G5" t="str">
-        <v>TRUE</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="str">
-        <v>DUMMY</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Sachin@578</v>
-      </c>
-      <c r="D6" t="str">
-        <v>sach@example.com</v>
-      </c>
-      <c r="E6" t="str">
-        <v>test</v>
-      </c>
-      <c r="F6" t="str">
-        <v>wrongpass</v>
-      </c>
-      <c r="G6" t="str">
-        <v>FALSE</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="str">
-        <v>CR01</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Sachin@578</v>
-      </c>
-      <c r="D7" t="str">
-        <v>cr01@example.com</v>
-      </c>
-      <c r="E7" t="str">
-        <v>admin</v>
-      </c>
-      <c r="F7" t="str">
-        <v>stage</v>
-      </c>
-      <c r="G7" t="str">
-        <v>TRUE</v>
-      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError sqref="A1:G7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/test-data/users.xlsx
+++ b/test-data/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Automation Project\WebWish 2\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F6DEFE-77CF-4589-A9C5-05691260E177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F57D65D-2669-48E7-AD4F-CDF654F9DCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
   <si>
     <t>index</t>
   </si>
@@ -76,22 +76,10 @@
     <t>dev</t>
   </si>
   <si>
-    <t>STAGE_USER</t>
-  </si>
-  <si>
-    <t>Stage@123</t>
-  </si>
-  <si>
     <t>stageuser@example.com</t>
   </si>
   <si>
     <t>stage</t>
-  </si>
-  <si>
-    <t>PROD_USER</t>
-  </si>
-  <si>
-    <t>Prod@123</t>
   </si>
   <si>
     <t>produser@example.com</t>
@@ -122,10 +110,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -169,15 +165,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -516,7 +515,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
@@ -524,7 +523,7 @@
     <col min="5" max="5" width="5.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,7 +546,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -570,7 +569,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -593,58 +592,58 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
@@ -653,33 +652,33 @@
         <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>12</v>
@@ -821,9 +820,13 @@
       <c r="G22" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{3B4AB230-B5E7-485C-8B23-2CD921A708C9}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{F79691C4-AC57-4AF2-BEB3-6C948DEF54BC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G3 A6:G7 A4 D4:G4 A5 D5:G5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>